--- a/public/StructureDefinition-pghd-observation-scored-assessment.xlsx
+++ b/public/StructureDefinition-pghd-observation-scored-assessment.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-observation-scored-assessment.xlsx
+++ b/public/StructureDefinition-pghd-observation-scored-assessment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6362" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6362" uniqueCount="676">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6581,7 +6584,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6615,7 +6618,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6692,10 +6695,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6812,10 +6815,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6932,10 +6935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7052,10 +7055,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7174,13 +7177,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7298,7 +7301,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>307</v>
@@ -7416,7 +7419,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>309</v>
@@ -7536,7 +7539,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>311</v>
@@ -7581,7 +7584,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7658,10 +7661,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7778,10 +7781,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7898,10 +7901,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8018,10 +8021,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8140,10 +8143,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8262,10 +8265,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8288,19 +8291,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8349,7 +8352,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8364,19 +8367,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8384,10 +8387,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8410,16 +8413,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8469,7 +8472,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8493,10 +8496,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8504,14 +8507,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8530,19 +8533,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8591,7 +8594,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8606,19 +8609,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8626,14 +8629,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8652,19 +8655,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8713,7 +8716,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8728,19 +8731,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8748,10 +8751,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8774,16 +8777,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8833,7 +8836,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8854,13 +8857,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8868,10 +8871,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8894,17 +8897,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8953,7 +8956,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8968,19 +8971,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8988,10 +8991,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9014,19 +9017,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9075,7 +9078,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9084,7 +9087,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9093,27 +9096,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9139,16 +9142,16 @@
         <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9173,13 +9176,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9197,7 +9200,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9206,7 +9209,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9221,7 +9224,7 @@
         <v>135</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9232,14 +9235,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9261,16 +9264,16 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9295,13 +9298,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9319,7 +9322,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9337,27 +9340,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9380,19 +9383,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9441,7 +9444,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9462,10 +9465,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9476,10 +9479,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9505,13 +9508,13 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9540,10 +9543,10 @@
         <v>290</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9561,7 +9564,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9579,27 +9582,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9625,16 +9628,16 @@
         <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9662,10 +9665,10 @@
         <v>290</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9683,7 +9686,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9704,10 +9707,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9721,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9744,16 +9747,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9803,7 +9806,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9821,27 +9824,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9864,16 +9867,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9923,7 +9926,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9941,27 +9944,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9984,19 +9987,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10045,7 +10048,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10057,7 +10060,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10066,10 +10069,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10080,10 +10083,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10198,10 +10201,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10318,14 +10321,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10347,10 +10350,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>141</v>
@@ -10405,7 +10408,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10440,10 +10443,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10466,13 +10469,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10523,7 +10526,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10532,7 +10535,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10544,10 +10547,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10558,10 +10561,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10584,13 +10587,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10641,7 +10644,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10650,7 +10653,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10662,10 +10665,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10676,10 +10679,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10705,16 +10708,16 @@
         <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10742,10 +10745,10 @@
         <v>116</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10763,7 +10766,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10781,13 +10784,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10798,10 +10801,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10827,16 +10830,16 @@
         <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10864,10 +10867,10 @@
         <v>290</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10885,7 +10888,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10903,13 +10906,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10920,10 +10923,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10946,17 +10949,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11005,7 +11008,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11029,7 +11032,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11040,10 +11043,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11069,10 +11072,10 @@
         <v>205</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11123,7 +11126,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11144,10 +11147,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11158,10 +11161,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11184,16 +11187,16 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11243,7 +11246,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11264,10 +11267,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11278,10 +11281,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11304,16 +11307,16 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11363,7 +11366,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11384,10 +11387,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11398,10 +11401,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11424,19 +11427,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11473,7 +11476,7 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11483,7 +11486,7 @@
         <v>198</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11504,10 +11507,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11518,10 +11521,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11636,10 +11639,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11756,14 +11759,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11785,10 +11788,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
@@ -11843,7 +11846,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11878,10 +11881,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11907,13 +11910,13 @@
         <v>190</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>289</v>
@@ -11965,7 +11968,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>92</v>
@@ -11983,7 +11986,7 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>295</v>
@@ -12000,10 +12003,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12026,19 +12029,19 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12087,7 +12090,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12105,27 +12108,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12151,16 +12154,16 @@
         <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12185,13 +12188,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12209,7 +12212,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12218,7 +12221,7 @@
         <v>92</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>104</v>
@@ -12233,7 +12236,7 @@
         <v>135</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12244,14 +12247,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12273,16 +12276,16 @@
         <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12307,13 +12310,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12331,7 +12334,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12349,27 +12352,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12395,16 +12398,16 @@
         <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12453,7 +12456,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12474,10 +12477,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12488,13 +12491,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
@@ -12516,19 +12519,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12577,7 +12580,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12598,10 +12601,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12612,10 +12615,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12730,10 +12733,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12850,14 +12853,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12879,10 +12882,10 @@
         <v>138</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>141</v>
@@ -12937,7 +12940,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12972,10 +12975,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13001,13 +13004,13 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>289</v>
@@ -13039,7 +13042,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13057,7 +13060,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>92</v>
@@ -13075,7 +13078,7 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>295</v>
@@ -13092,10 +13095,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13210,10 +13213,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13330,10 +13333,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13452,10 +13455,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13570,10 +13573,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13690,10 +13693,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13735,7 +13738,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>82</v>
@@ -13812,10 +13815,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13932,10 +13935,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14052,10 +14055,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14172,10 +14175,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14294,10 +14297,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14416,10 +14419,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14442,19 +14445,19 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14503,7 +14506,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14521,27 +14524,27 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14567,16 +14570,16 @@
         <v>190</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14601,13 +14604,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14625,7 +14628,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14634,7 +14637,7 @@
         <v>92</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>104</v>
@@ -14649,7 +14652,7 @@
         <v>135</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14660,14 +14663,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14689,16 +14692,16 @@
         <v>190</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14723,13 +14726,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14747,7 +14750,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14765,27 +14768,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14811,16 +14814,16 @@
         <v>83</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14869,7 +14872,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14890,10 +14893,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14904,13 +14907,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>82</v>
@@ -14932,19 +14935,19 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14993,7 +14996,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15014,10 +15017,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15028,10 +15031,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15146,10 +15149,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15266,14 +15269,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15295,10 +15298,10 @@
         <v>138</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>141</v>
@@ -15353,7 +15356,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15388,10 +15391,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15417,13 +15420,13 @@
         <v>190</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>289</v>
@@ -15455,7 +15458,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15473,7 +15476,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>92</v>
@@ -15491,7 +15494,7 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>295</v>
@@ -15508,10 +15511,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15626,10 +15629,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15746,10 +15749,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15868,10 +15871,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15986,10 +15989,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16106,10 +16109,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16151,7 +16154,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>82</v>
@@ -16228,10 +16231,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16348,10 +16351,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16391,7 +16394,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>82</v>
@@ -16468,10 +16471,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16588,10 +16591,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16710,10 +16713,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16832,10 +16835,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16861,16 +16864,16 @@
         <v>190</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16899,7 +16902,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -16917,7 +16920,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16935,27 +16938,27 @@
         <v>82</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17070,10 +17073,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17190,10 +17193,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17312,10 +17315,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17430,10 +17433,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17550,10 +17553,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17595,7 +17598,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>82</v>
@@ -17672,10 +17675,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17792,10 +17795,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17912,10 +17915,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18032,10 +18035,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18154,10 +18157,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18276,10 +18279,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18305,16 +18308,16 @@
         <v>190</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18339,13 +18342,13 @@
         <v>82</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>82</v>
@@ -18363,7 +18366,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18372,7 +18375,7 @@
         <v>92</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>104</v>
@@ -18387,7 +18390,7 @@
         <v>135</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18398,14 +18401,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18427,16 +18430,16 @@
         <v>190</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18461,13 +18464,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -18485,7 +18488,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18503,27 +18506,27 @@
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18549,16 +18552,16 @@
         <v>83</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18607,7 +18610,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18628,10 +18631,10 @@
         <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18642,13 +18645,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>82</v>
@@ -18670,19 +18673,19 @@
         <v>93</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18731,7 +18734,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18752,10 +18755,10 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18766,10 +18769,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18884,10 +18887,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19004,14 +19007,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19033,10 +19036,10 @@
         <v>138</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>141</v>
@@ -19091,7 +19094,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19126,10 +19129,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19155,13 +19158,13 @@
         <v>190</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O139" t="s" s="2">
         <v>289</v>
@@ -19193,7 +19196,7 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19211,7 +19214,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>92</v>
@@ -19229,7 +19232,7 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>295</v>
@@ -19246,10 +19249,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19364,10 +19367,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19484,10 +19487,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19606,10 +19609,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19724,10 +19727,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19844,10 +19847,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19889,7 +19892,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>82</v>
@@ -19966,10 +19969,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20086,10 +20089,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20129,7 +20132,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>82</v>
@@ -20206,10 +20209,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20326,10 +20329,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20448,10 +20451,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20570,10 +20573,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20599,16 +20602,16 @@
         <v>190</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20637,7 +20640,7 @@
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>82</v>
@@ -20655,7 +20658,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20673,27 +20676,27 @@
         <v>82</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20808,10 +20811,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20928,10 +20931,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21050,10 +21053,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21168,10 +21171,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21288,10 +21291,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21336,7 +21339,7 @@
         <v>82</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>82</v>
@@ -21410,10 +21413,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21530,10 +21533,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21650,10 +21653,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21770,10 +21773,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21892,10 +21895,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22014,10 +22017,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22043,16 +22046,16 @@
         <v>190</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22077,13 +22080,13 @@
         <v>82</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22101,7 +22104,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22110,7 +22113,7 @@
         <v>92</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>104</v>
@@ -22125,7 +22128,7 @@
         <v>135</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22136,14 +22139,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -22165,16 +22168,16 @@
         <v>190</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22199,13 +22202,13 @@
         <v>82</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22223,7 +22226,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22241,27 +22244,27 @@
         <v>82</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22287,16 +22290,16 @@
         <v>83</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22345,7 +22348,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22366,10 +22369,10 @@
         <v>82</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
